--- a/data/stages.xlsx
+++ b/data/stages.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
         <v/>
       </c>
       <c r="E2" t="str">
-        <v>mf_001</v>
+        <v>mf_003</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2" t="str">
-        <v>你的第一场比赛</v>
+        <v>你的第一场比赛，击败菜鸟队证明实力</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +450,7 @@
         <v>stage_002</v>
       </c>
       <c r="B3" t="str">
-        <v>城市联赛</v>
+        <v>街头争霸</v>
       </c>
       <c r="C3" t="str">
         <v>ai_team_002</v>
@@ -459,13 +459,13 @@
         <v>stage_001</v>
       </c>
       <c r="E3" t="str">
-        <v>fw_001</v>
+        <v>df_003</v>
       </c>
       <c r="F3">
         <v>200</v>
       </c>
       <c r="G3" t="str">
-        <v>面对更强的对手</v>
+        <v>街头混混来势汹汹，小心应对</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         <v>stage_003</v>
       </c>
       <c r="B4" t="str">
-        <v>冠军之路</v>
+        <v>武林大会</v>
       </c>
       <c r="C4" t="str">
         <v>ai_team_003</v>
@@ -485,15 +485,61 @@
         <v>fw_003</v>
       </c>
       <c r="F4">
+        <v>350</v>
+      </c>
+      <c r="G4" t="str">
+        <v>武当少年队功力深厚，硬仗开始</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>stage_004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>少林争锋</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ai_team_004</v>
+      </c>
+      <c r="D5" t="str">
+        <v>stage_003</v>
+      </c>
+      <c r="E5" t="str">
+        <v>gk_002</v>
+      </c>
+      <c r="F5">
         <v>500</v>
       </c>
-      <c r="G4" t="str">
-        <v>终极挑战</v>
+      <c r="G5" t="str">
+        <v>少林精英全员出击，生死一战</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>stage_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>天下第一</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ai_team_005</v>
+      </c>
+      <c r="D6" t="str">
+        <v>stage_004</v>
+      </c>
+      <c r="E6" t="str">
+        <v>fw_005</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6" t="str">
+        <v>终极挑战！击败天下第一队登顶巅峰</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>